--- a/testcases/Passed_Test_Cases.xlsx
+++ b/testcases/Passed_Test_Cases.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E391"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,8 +505,10 @@
           <t>Android Appium Authentication Spec #01</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>0.06</v>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -528,8 +530,10 @@
           <t>Android Appium Authentication Spec #02</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>0.08</v>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,8 +555,10 @@
           <t>Android Appium Authentication Spec #03</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>0.1</v>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -574,8 +580,10 @@
           <t>Android Appium Authentication Spec #04</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>0.12</v>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -597,8 +605,10 @@
           <t>Android Appium Authentication Spec #05</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>0.04</v>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -620,8 +630,10 @@
           <t>Android Appium Authentication Spec #06</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>0.06</v>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -643,8 +655,10 @@
           <t>Android Appium Authentication Spec #07</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>0.08</v>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -666,8 +680,10 @@
           <t>Android Appium Authentication Spec #08</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>0.1</v>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -689,8 +705,10 @@
           <t>Android Appium Authentication Spec #09</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>0.12</v>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -712,8 +730,10 @@
           <t>Android Appium Authentication Spec #10</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>0.04</v>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -735,8 +755,10 @@
           <t>Android Appium Authentication Spec #11</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>0.06</v>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -758,8 +780,10 @@
           <t>Android Appium Authentication Spec #12</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>0.08</v>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -781,8 +805,10 @@
           <t>Android Appium Authentication Spec #13</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>0.1</v>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -804,8 +830,10 @@
           <t>Android Appium Authentication Spec #14</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>0.12</v>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -827,8 +855,10 @@
           <t>Android Appium Authentication Spec #15</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
-        <v>0.04</v>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -850,8 +880,10 @@
           <t>Android Appium Authentication Spec #16</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
-        <v>0.06</v>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -873,8 +905,10 @@
           <t>Android Appium Authentication Spec #17</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>0.08</v>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -896,8 +930,10 @@
           <t>Android Appium Authentication Spec #18</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>0.1</v>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -919,8 +955,10 @@
           <t>Android Appium Authentication Spec #19</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
-        <v>0.12</v>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -942,8 +980,10 @@
           <t>Android Appium Authentication Spec #20</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>0.04</v>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -965,8 +1005,10 @@
           <t>Android Appium Authentication Spec #21</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
-        <v>0.06</v>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -988,8 +1030,10 @@
           <t>Android Appium Authentication Spec #22</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
-        <v>0.08</v>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1011,8 +1055,10 @@
           <t>Android Appium Authentication Spec #23</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
-        <v>0.1</v>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1034,8 +1080,10 @@
           <t>Android Appium Authentication Spec #24</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>0.12</v>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1057,8 +1105,10 @@
           <t>Android Appium Authentication Spec #25</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
-        <v>0.04</v>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1080,8 +1130,10 @@
           <t>Android Appium Authentication Spec #26</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
-        <v>0.06</v>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1103,8 +1155,10 @@
           <t>Android Appium Authentication Spec #27</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
-        <v>0.08</v>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1126,8 +1180,10 @@
           <t>Android Appium Authentication Spec #28</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
-        <v>0.1</v>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1149,8 +1205,10 @@
           <t>Android Appium Authentication Spec #29</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
-        <v>0.12</v>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1172,8 +1230,10 @@
           <t>Android Appium Authentication Spec #30</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
-        <v>0.04</v>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1195,8 +1255,10 @@
           <t>Android Appium Authentication Spec #31</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
-        <v>0.06</v>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1218,8 +1280,10 @@
           <t>Android Appium Authentication Spec #32</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
-        <v>0.08</v>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1241,8 +1305,10 @@
           <t>Android Appium Authentication Spec #33</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
-        <v>0.1</v>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1264,8 +1330,10 @@
           <t>Android Appium Authentication Spec #34</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
-        <v>0.12</v>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1287,8 +1355,10 @@
           <t>Android Appium Authentication Spec #35</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
-        <v>0.04</v>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1310,8 +1380,10 @@
           <t>Android Appium Authentication Spec #36</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
-        <v>0.06</v>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1333,8 +1405,10 @@
           <t>Android Appium Authentication Spec #37</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
-        <v>0.08</v>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1356,8 +1430,10 @@
           <t>Android Appium Authentication Spec #38</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
-        <v>0.1</v>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1379,8 +1455,10 @@
           <t>Android Appium Authentication Spec #39</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
-        <v>0.12</v>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1402,8 +1480,10 @@
           <t>Android Appium Authorization Spec #01</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
-        <v>0.06</v>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1425,8 +1505,10 @@
           <t>Android Appium Authorization Spec #02</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
-        <v>0.08</v>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1448,8 +1530,10 @@
           <t>Android Appium Authorization Spec #03</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
-        <v>0.1</v>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1471,8 +1555,10 @@
           <t>Android Appium Authorization Spec #04</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
-        <v>0.12</v>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1494,8 +1580,10 @@
           <t>Android Appium Authorization Spec #05</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
-        <v>0.04</v>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1517,8 +1605,10 @@
           <t>Android Appium Authorization Spec #06</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
-        <v>0.06</v>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -1540,8 +1630,10 @@
           <t>Android Appium Authorization Spec #07</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
-        <v>0.08</v>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -1563,8 +1655,10 @@
           <t>Android Appium Authorization Spec #08</t>
         </is>
       </c>
-      <c r="D48" s="4" t="n">
-        <v>0.1</v>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -1586,8 +1680,10 @@
           <t>Android Appium Authorization Spec #09</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
-        <v>0.12</v>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -1609,8 +1705,10 @@
           <t>Android Appium Authorization Spec #10</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
-        <v>0.04</v>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -1632,8 +1730,10 @@
           <t>Android Appium Authorization Spec #11</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
-        <v>0.06</v>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -1655,8 +1755,10 @@
           <t>Android Appium Authorization Spec #12</t>
         </is>
       </c>
-      <c r="D52" s="4" t="n">
-        <v>0.08</v>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -1678,8 +1780,10 @@
           <t>Android Appium Authorization Spec #13</t>
         </is>
       </c>
-      <c r="D53" s="4" t="n">
-        <v>0.1</v>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -1701,8 +1805,10 @@
           <t>Android Appium Authorization Spec #14</t>
         </is>
       </c>
-      <c r="D54" s="4" t="n">
-        <v>0.12</v>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -1724,8 +1830,10 @@
           <t>Android Appium Authorization Spec #15</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n">
-        <v>0.04</v>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -1747,8 +1855,10 @@
           <t>Android Appium Authorization Spec #16</t>
         </is>
       </c>
-      <c r="D56" s="4" t="n">
-        <v>0.06</v>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -1770,8 +1880,10 @@
           <t>Android Appium Authorization Spec #17</t>
         </is>
       </c>
-      <c r="D57" s="4" t="n">
-        <v>0.08</v>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -1793,8 +1905,10 @@
           <t>Android Appium Authorization Spec #18</t>
         </is>
       </c>
-      <c r="D58" s="4" t="n">
-        <v>0.1</v>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -1816,8 +1930,10 @@
           <t>Android Appium Authorization Spec #19</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
-        <v>0.12</v>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -1839,8 +1955,10 @@
           <t>Android Appium Authorization Spec #20</t>
         </is>
       </c>
-      <c r="D60" s="4" t="n">
-        <v>0.04</v>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -1862,8 +1980,10 @@
           <t>Android Appium Authorization Spec #21</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n">
-        <v>0.06</v>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -1885,8 +2005,10 @@
           <t>Android Appium Authorization Spec #22</t>
         </is>
       </c>
-      <c r="D62" s="4" t="n">
-        <v>0.08</v>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -1908,8 +2030,10 @@
           <t>Android Appium Authorization Spec #23</t>
         </is>
       </c>
-      <c r="D63" s="4" t="n">
-        <v>0.1</v>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -1931,8 +2055,10 @@
           <t>Android Appium Authorization Spec #24</t>
         </is>
       </c>
-      <c r="D64" s="4" t="n">
-        <v>0.12</v>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -1954,8 +2080,10 @@
           <t>Android Appium Authorization Spec #25</t>
         </is>
       </c>
-      <c r="D65" s="4" t="n">
-        <v>0.04</v>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -1977,8 +2105,10 @@
           <t>Android Appium Authorization Spec #26</t>
         </is>
       </c>
-      <c r="D66" s="4" t="n">
-        <v>0.06</v>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2000,8 +2130,10 @@
           <t>Android Appium Authorization Spec #27</t>
         </is>
       </c>
-      <c r="D67" s="4" t="n">
-        <v>0.08</v>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2023,8 +2155,10 @@
           <t>Android Appium Authorization Spec #28</t>
         </is>
       </c>
-      <c r="D68" s="4" t="n">
-        <v>0.1</v>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2046,8 +2180,10 @@
           <t>Android Appium Authorization Spec #29</t>
         </is>
       </c>
-      <c r="D69" s="4" t="n">
-        <v>0.12</v>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2069,8 +2205,10 @@
           <t>Android Appium Authorization Spec #30</t>
         </is>
       </c>
-      <c r="D70" s="4" t="n">
-        <v>0.04</v>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2092,8 +2230,10 @@
           <t>Android Appium Registration Spec #01</t>
         </is>
       </c>
-      <c r="D71" s="4" t="n">
-        <v>0.06</v>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2115,8 +2255,10 @@
           <t>Android Appium Registration Spec #02</t>
         </is>
       </c>
-      <c r="D72" s="4" t="n">
-        <v>0.08</v>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2138,8 +2280,10 @@
           <t>Android Appium Registration Spec #03</t>
         </is>
       </c>
-      <c r="D73" s="4" t="n">
-        <v>0.1</v>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2161,8 +2305,10 @@
           <t>Android Appium Registration Spec #04</t>
         </is>
       </c>
-      <c r="D74" s="4" t="n">
-        <v>0.12</v>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -2184,8 +2330,10 @@
           <t>Android Appium Registration Spec #05</t>
         </is>
       </c>
-      <c r="D75" s="4" t="n">
-        <v>0.04</v>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2207,8 +2355,10 @@
           <t>Android Appium Registration Spec #06</t>
         </is>
       </c>
-      <c r="D76" s="4" t="n">
-        <v>0.06</v>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -2230,8 +2380,10 @@
           <t>Android Appium Registration Spec #07</t>
         </is>
       </c>
-      <c r="D77" s="4" t="n">
-        <v>0.08</v>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -2253,8 +2405,10 @@
           <t>Android Appium Registration Spec #08</t>
         </is>
       </c>
-      <c r="D78" s="4" t="n">
-        <v>0.1</v>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -2276,8 +2430,10 @@
           <t>Android Appium Registration Spec #09</t>
         </is>
       </c>
-      <c r="D79" s="4" t="n">
-        <v>0.12</v>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -2299,8 +2455,10 @@
           <t>Android Appium Registration Spec #11</t>
         </is>
       </c>
-      <c r="D80" s="4" t="n">
-        <v>0.06</v>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -2322,8 +2480,10 @@
           <t>Android Appium Registration Spec #12</t>
         </is>
       </c>
-      <c r="D81" s="4" t="n">
-        <v>0.08</v>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -2345,8 +2505,10 @@
           <t>Android Appium Registration Spec #13</t>
         </is>
       </c>
-      <c r="D82" s="4" t="n">
-        <v>0.1</v>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -2368,8 +2530,10 @@
           <t>Android Appium Registration Spec #14</t>
         </is>
       </c>
-      <c r="D83" s="4" t="n">
-        <v>0.12</v>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -2391,8 +2555,10 @@
           <t>Android Appium Registration Spec #15</t>
         </is>
       </c>
-      <c r="D84" s="4" t="n">
-        <v>0.04</v>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -2414,8 +2580,10 @@
           <t>Android Appium Registration Spec #16</t>
         </is>
       </c>
-      <c r="D85" s="4" t="n">
-        <v>0.06</v>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -2437,8 +2605,10 @@
           <t>Android Appium Registration Spec #17</t>
         </is>
       </c>
-      <c r="D86" s="4" t="n">
-        <v>0.08</v>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -2460,8 +2630,10 @@
           <t>Android Appium Registration Spec #18</t>
         </is>
       </c>
-      <c r="D87" s="4" t="n">
-        <v>0.1</v>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -2483,8 +2655,10 @@
           <t>Android Appium Registration Spec #19</t>
         </is>
       </c>
-      <c r="D88" s="4" t="n">
-        <v>0.12</v>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -2506,8 +2680,10 @@
           <t>Android Appium Registration Spec #20</t>
         </is>
       </c>
-      <c r="D89" s="4" t="n">
-        <v>0.04</v>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -2529,8 +2705,10 @@
           <t>Android Appium Profile Management Spec #01</t>
         </is>
       </c>
-      <c r="D90" s="4" t="n">
-        <v>0.06</v>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -2552,8 +2730,10 @@
           <t>Android Appium Profile Management Spec #02</t>
         </is>
       </c>
-      <c r="D91" s="4" t="n">
-        <v>0.08</v>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -2575,8 +2755,10 @@
           <t>Android Appium Profile Management Spec #03</t>
         </is>
       </c>
-      <c r="D92" s="4" t="n">
-        <v>0.1</v>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -2598,8 +2780,10 @@
           <t>Android Appium Profile Management Spec #04</t>
         </is>
       </c>
-      <c r="D93" s="4" t="n">
-        <v>0.12</v>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -2621,8 +2805,10 @@
           <t>Android Appium Profile Management Spec #05</t>
         </is>
       </c>
-      <c r="D94" s="4" t="n">
-        <v>0.04</v>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -2644,8 +2830,10 @@
           <t>Android Appium Profile Management Spec #06</t>
         </is>
       </c>
-      <c r="D95" s="4" t="n">
-        <v>0.06</v>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -2667,8 +2855,10 @@
           <t>Android Appium Profile Management Spec #07</t>
         </is>
       </c>
-      <c r="D96" s="4" t="n">
-        <v>0.08</v>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -2690,8 +2880,10 @@
           <t>Android Appium Profile Management Spec #08</t>
         </is>
       </c>
-      <c r="D97" s="4" t="n">
-        <v>0.1</v>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -2713,8 +2905,10 @@
           <t>Android Appium Profile Management Spec #09</t>
         </is>
       </c>
-      <c r="D98" s="4" t="n">
-        <v>0.12</v>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -2736,8 +2930,10 @@
           <t>Android Appium Profile Management Spec #10</t>
         </is>
       </c>
-      <c r="D99" s="4" t="n">
-        <v>0.04</v>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -2759,8 +2955,10 @@
           <t>Android Appium Profile Management Spec #11</t>
         </is>
       </c>
-      <c r="D100" s="4" t="n">
-        <v>0.06</v>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -2782,8 +2980,10 @@
           <t>Android Appium Profile Management Spec #12</t>
         </is>
       </c>
-      <c r="D101" s="4" t="n">
-        <v>0.08</v>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -2805,8 +3005,10 @@
           <t>Android Appium Profile Management Spec #13</t>
         </is>
       </c>
-      <c r="D102" s="4" t="n">
-        <v>0.1</v>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -2828,8 +3030,10 @@
           <t>Android Appium Profile Management Spec #14</t>
         </is>
       </c>
-      <c r="D103" s="4" t="n">
-        <v>0.12</v>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -2851,8 +3055,10 @@
           <t>Android Appium Profile Management Spec #15</t>
         </is>
       </c>
-      <c r="D104" s="4" t="n">
-        <v>0.04</v>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -2874,8 +3080,10 @@
           <t>Android Appium Profile Management Spec #16</t>
         </is>
       </c>
-      <c r="D105" s="4" t="n">
-        <v>0.06</v>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -2897,8 +3105,10 @@
           <t>Android Appium Profile Management Spec #17</t>
         </is>
       </c>
-      <c r="D106" s="4" t="n">
-        <v>0.08</v>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -2920,8 +3130,10 @@
           <t>Android Appium Profile Management Spec #18</t>
         </is>
       </c>
-      <c r="D107" s="4" t="n">
-        <v>0.1</v>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -2943,8 +3155,10 @@
           <t>Android Appium Profile Management Spec #19</t>
         </is>
       </c>
-      <c r="D108" s="4" t="n">
-        <v>0.12</v>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -2966,8 +3180,10 @@
           <t>Android Appium Profile Management Spec #20</t>
         </is>
       </c>
-      <c r="D109" s="4" t="n">
-        <v>0.04</v>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -2989,8 +3205,10 @@
           <t>Android Appium Navigation Spec #01</t>
         </is>
       </c>
-      <c r="D110" s="4" t="n">
-        <v>0.06</v>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -3012,8 +3230,10 @@
           <t>Android Appium Navigation Spec #02</t>
         </is>
       </c>
-      <c r="D111" s="4" t="n">
-        <v>0.08</v>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -3035,8 +3255,10 @@
           <t>Android Appium Navigation Spec #03</t>
         </is>
       </c>
-      <c r="D112" s="4" t="n">
-        <v>0.1</v>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -3058,8 +3280,10 @@
           <t>Android Appium Navigation Spec #04</t>
         </is>
       </c>
-      <c r="D113" s="4" t="n">
-        <v>0.12</v>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -3081,8 +3305,10 @@
           <t>Android Appium Navigation Spec #05</t>
         </is>
       </c>
-      <c r="D114" s="4" t="n">
-        <v>0.04</v>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -3104,8 +3330,10 @@
           <t>Android Appium Navigation Spec #06</t>
         </is>
       </c>
-      <c r="D115" s="4" t="n">
-        <v>0.06</v>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -3127,8 +3355,10 @@
           <t>Android Appium Navigation Spec #07</t>
         </is>
       </c>
-      <c r="D116" s="4" t="n">
-        <v>0.08</v>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -3150,8 +3380,10 @@
           <t>Android Appium Navigation Spec #08</t>
         </is>
       </c>
-      <c r="D117" s="4" t="n">
-        <v>0.1</v>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
@@ -3173,8 +3405,10 @@
           <t>Android Appium Navigation Spec #09</t>
         </is>
       </c>
-      <c r="D118" s="4" t="n">
-        <v>0.12</v>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
@@ -3196,8 +3430,10 @@
           <t>Android Appium Navigation Spec #11</t>
         </is>
       </c>
-      <c r="D119" s="4" t="n">
-        <v>0.06</v>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
@@ -3219,8 +3455,10 @@
           <t>Android Appium Navigation Spec #12</t>
         </is>
       </c>
-      <c r="D120" s="4" t="n">
-        <v>0.08</v>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
@@ -3242,8 +3480,10 @@
           <t>Android Appium Navigation Spec #13</t>
         </is>
       </c>
-      <c r="D121" s="4" t="n">
-        <v>0.1</v>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
@@ -3265,8 +3505,10 @@
           <t>Android Appium Navigation Spec #14</t>
         </is>
       </c>
-      <c r="D122" s="4" t="n">
-        <v>0.12</v>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
@@ -3288,8 +3530,10 @@
           <t>Android Appium Navigation Spec #15</t>
         </is>
       </c>
-      <c r="D123" s="4" t="n">
-        <v>0.04</v>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
@@ -3311,8 +3555,10 @@
           <t>Android Appium Navigation Spec #16</t>
         </is>
       </c>
-      <c r="D124" s="4" t="n">
-        <v>0.06</v>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
@@ -3334,8 +3580,10 @@
           <t>Android Appium Navigation Spec #17</t>
         </is>
       </c>
-      <c r="D125" s="4" t="n">
-        <v>0.08</v>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
@@ -3357,8 +3605,10 @@
           <t>Android Appium Navigation Spec #18</t>
         </is>
       </c>
-      <c r="D126" s="4" t="n">
-        <v>0.1</v>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
@@ -3380,8 +3630,10 @@
           <t>Android Appium Navigation Spec #19</t>
         </is>
       </c>
-      <c r="D127" s="4" t="n">
-        <v>0.12</v>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
@@ -3403,8 +3655,10 @@
           <t>Android Appium Navigation Spec #20</t>
         </is>
       </c>
-      <c r="D128" s="4" t="n">
-        <v>0.04</v>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
@@ -3426,8 +3680,10 @@
           <t>Android Appium Navigation Spec #21</t>
         </is>
       </c>
-      <c r="D129" s="4" t="n">
-        <v>0.06</v>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
@@ -3449,8 +3705,10 @@
           <t>Android Appium Navigation Spec #22</t>
         </is>
       </c>
-      <c r="D130" s="4" t="n">
-        <v>0.08</v>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
@@ -3472,8 +3730,10 @@
           <t>Android Appium Navigation Spec #23</t>
         </is>
       </c>
-      <c r="D131" s="4" t="n">
-        <v>0.1</v>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
@@ -3495,8 +3755,10 @@
           <t>Android Appium Navigation Spec #24</t>
         </is>
       </c>
-      <c r="D132" s="4" t="n">
-        <v>0.12</v>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -3518,8 +3780,10 @@
           <t>Android Appium Navigation Spec #25</t>
         </is>
       </c>
-      <c r="D133" s="4" t="n">
-        <v>0.04</v>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -3541,8 +3805,10 @@
           <t>Android Appium Navigation Spec #26</t>
         </is>
       </c>
-      <c r="D134" s="4" t="n">
-        <v>0.06</v>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
@@ -3564,8 +3830,10 @@
           <t>Android Appium Navigation Spec #27</t>
         </is>
       </c>
-      <c r="D135" s="4" t="n">
-        <v>0.08</v>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -3587,8 +3855,10 @@
           <t>Android Appium Navigation Spec #28</t>
         </is>
       </c>
-      <c r="D136" s="4" t="n">
-        <v>0.1</v>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -3610,8 +3880,10 @@
           <t>Android Appium Navigation Spec #29</t>
         </is>
       </c>
-      <c r="D137" s="4" t="n">
-        <v>0.12</v>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
@@ -3633,8 +3905,10 @@
           <t>Android Appium Navigation Spec #30</t>
         </is>
       </c>
-      <c r="D138" s="4" t="n">
-        <v>0.04</v>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -3656,8 +3930,10 @@
           <t>Android Appium Dashboard Spec #01</t>
         </is>
       </c>
-      <c r="D139" s="4" t="n">
-        <v>0.06</v>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
@@ -3679,8 +3955,10 @@
           <t>Android Appium Dashboard Spec #02</t>
         </is>
       </c>
-      <c r="D140" s="4" t="n">
-        <v>0.08</v>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
@@ -3702,8 +3980,10 @@
           <t>Android Appium Dashboard Spec #03</t>
         </is>
       </c>
-      <c r="D141" s="4" t="n">
-        <v>0.1</v>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
@@ -3725,8 +4005,10 @@
           <t>Android Appium Dashboard Spec #04</t>
         </is>
       </c>
-      <c r="D142" s="4" t="n">
-        <v>0.12</v>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
@@ -3748,8 +4030,10 @@
           <t>Android Appium Dashboard Spec #05</t>
         </is>
       </c>
-      <c r="D143" s="4" t="n">
-        <v>0.04</v>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
@@ -3771,8 +4055,10 @@
           <t>Android Appium Dashboard Spec #06</t>
         </is>
       </c>
-      <c r="D144" s="4" t="n">
-        <v>0.06</v>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -3794,8 +4080,10 @@
           <t>Android Appium Dashboard Spec #07</t>
         </is>
       </c>
-      <c r="D145" s="4" t="n">
-        <v>0.08</v>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
@@ -3817,8 +4105,10 @@
           <t>Android Appium Dashboard Spec #08</t>
         </is>
       </c>
-      <c r="D146" s="4" t="n">
-        <v>0.1</v>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -3840,8 +4130,10 @@
           <t>Android Appium Dashboard Spec #09</t>
         </is>
       </c>
-      <c r="D147" s="4" t="n">
-        <v>0.12</v>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
@@ -3863,8 +4155,10 @@
           <t>Android Appium Dashboard Spec #10</t>
         </is>
       </c>
-      <c r="D148" s="4" t="n">
-        <v>0.04</v>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
@@ -3886,8 +4180,10 @@
           <t>Android Appium Dashboard Spec #11</t>
         </is>
       </c>
-      <c r="D149" s="4" t="n">
-        <v>0.06</v>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
@@ -3909,8 +4205,10 @@
           <t>Android Appium Dashboard Spec #12</t>
         </is>
       </c>
-      <c r="D150" s="4" t="n">
-        <v>0.08</v>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
@@ -3932,8 +4230,10 @@
           <t>Android Appium Dashboard Spec #13</t>
         </is>
       </c>
-      <c r="D151" s="4" t="n">
-        <v>0.1</v>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -3955,8 +4255,10 @@
           <t>Android Appium Dashboard Spec #14</t>
         </is>
       </c>
-      <c r="D152" s="4" t="n">
-        <v>0.12</v>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -3978,8 +4280,10 @@
           <t>Android Appium Dashboard Spec #15</t>
         </is>
       </c>
-      <c r="D153" s="4" t="n">
-        <v>0.04</v>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
@@ -4001,8 +4305,10 @@
           <t>Android Appium Dashboard Spec #16</t>
         </is>
       </c>
-      <c r="D154" s="4" t="n">
-        <v>0.06</v>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
@@ -4024,8 +4330,10 @@
           <t>Android Appium Dashboard Spec #17</t>
         </is>
       </c>
-      <c r="D155" s="4" t="n">
-        <v>0.08</v>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
@@ -4047,8 +4355,10 @@
           <t>Android Appium Dashboard Spec #18</t>
         </is>
       </c>
-      <c r="D156" s="4" t="n">
-        <v>0.1</v>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
@@ -4070,8 +4380,10 @@
           <t>Android Appium Dashboard Spec #19</t>
         </is>
       </c>
-      <c r="D157" s="4" t="n">
-        <v>0.12</v>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
@@ -4093,8 +4405,10 @@
           <t>Android Appium Forms Spec #01</t>
         </is>
       </c>
-      <c r="D158" s="4" t="n">
-        <v>0.06</v>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
@@ -4116,8 +4430,10 @@
           <t>Android Appium Forms Spec #02</t>
         </is>
       </c>
-      <c r="D159" s="4" t="n">
-        <v>0.08</v>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
@@ -4139,8 +4455,10 @@
           <t>Android Appium Forms Spec #03</t>
         </is>
       </c>
-      <c r="D160" s="4" t="n">
-        <v>0.1</v>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
@@ -4162,8 +4480,10 @@
           <t>Android Appium Forms Spec #04</t>
         </is>
       </c>
-      <c r="D161" s="4" t="n">
-        <v>0.12</v>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
@@ -4185,8 +4505,10 @@
           <t>Android Appium Forms Spec #05</t>
         </is>
       </c>
-      <c r="D162" s="4" t="n">
-        <v>0.04</v>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
@@ -4208,8 +4530,10 @@
           <t>Android Appium Forms Spec #06</t>
         </is>
       </c>
-      <c r="D163" s="4" t="n">
-        <v>0.06</v>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -4231,8 +4555,10 @@
           <t>Android Appium Forms Spec #07</t>
         </is>
       </c>
-      <c r="D164" s="4" t="n">
-        <v>0.08</v>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
@@ -4254,8 +4580,10 @@
           <t>Android Appium Forms Spec #08</t>
         </is>
       </c>
-      <c r="D165" s="4" t="n">
-        <v>0.1</v>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
@@ -4277,8 +4605,10 @@
           <t>Android Appium Forms Spec #09</t>
         </is>
       </c>
-      <c r="D166" s="4" t="n">
-        <v>0.12</v>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
@@ -4300,8 +4630,10 @@
           <t>Android Appium Forms Spec #10</t>
         </is>
       </c>
-      <c r="D167" s="4" t="n">
-        <v>0.04</v>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
@@ -4323,8 +4655,10 @@
           <t>Android Appium Forms Spec #11</t>
         </is>
       </c>
-      <c r="D168" s="4" t="n">
-        <v>0.06</v>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
@@ -4346,8 +4680,10 @@
           <t>Android Appium Forms Spec #12</t>
         </is>
       </c>
-      <c r="D169" s="4" t="n">
-        <v>0.08</v>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
@@ -4369,8 +4705,10 @@
           <t>Android Appium Forms Spec #13</t>
         </is>
       </c>
-      <c r="D170" s="4" t="n">
-        <v>0.1</v>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -4392,8 +4730,10 @@
           <t>Android Appium Forms Spec #14</t>
         </is>
       </c>
-      <c r="D171" s="4" t="n">
-        <v>0.12</v>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -4415,8 +4755,10 @@
           <t>Android Appium Forms Spec #15</t>
         </is>
       </c>
-      <c r="D172" s="4" t="n">
-        <v>0.04</v>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
@@ -4438,8 +4780,10 @@
           <t>Android Appium Forms Spec #16</t>
         </is>
       </c>
-      <c r="D173" s="4" t="n">
-        <v>0.06</v>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -4461,8 +4805,10 @@
           <t>Android Appium Forms Spec #17</t>
         </is>
       </c>
-      <c r="D174" s="4" t="n">
-        <v>0.08</v>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
@@ -4484,8 +4830,10 @@
           <t>Android Appium Forms Spec #18</t>
         </is>
       </c>
-      <c r="D175" s="4" t="n">
-        <v>0.1</v>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
@@ -4507,8 +4855,10 @@
           <t>Android Appium Forms Spec #19</t>
         </is>
       </c>
-      <c r="D176" s="4" t="n">
-        <v>0.12</v>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
@@ -4530,8 +4880,10 @@
           <t>Android Appium Forms Spec #20</t>
         </is>
       </c>
-      <c r="D177" s="4" t="n">
-        <v>0.04</v>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
@@ -4553,8 +4905,10 @@
           <t>Android Appium Forms Spec #21</t>
         </is>
       </c>
-      <c r="D178" s="4" t="n">
-        <v>0.06</v>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
@@ -4576,8 +4930,10 @@
           <t>Android Appium Forms Spec #22</t>
         </is>
       </c>
-      <c r="D179" s="4" t="n">
-        <v>0.08</v>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
@@ -4599,8 +4955,10 @@
           <t>Android Appium Forms Spec #23</t>
         </is>
       </c>
-      <c r="D180" s="4" t="n">
-        <v>0.1</v>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
@@ -4622,8 +4980,10 @@
           <t>Android Appium Forms Spec #24</t>
         </is>
       </c>
-      <c r="D181" s="4" t="n">
-        <v>0.12</v>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
@@ -4645,8 +5005,10 @@
           <t>Android Appium Forms Spec #25</t>
         </is>
       </c>
-      <c r="D182" s="4" t="n">
-        <v>0.04</v>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
@@ -4668,8 +5030,10 @@
           <t>Android Appium Forms Spec #26</t>
         </is>
       </c>
-      <c r="D183" s="4" t="n">
-        <v>0.06</v>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
@@ -4691,8 +5055,10 @@
           <t>Android Appium Forms Spec #27</t>
         </is>
       </c>
-      <c r="D184" s="4" t="n">
-        <v>0.08</v>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
@@ -4714,8 +5080,10 @@
           <t>Android Appium Forms Spec #28</t>
         </is>
       </c>
-      <c r="D185" s="4" t="n">
-        <v>0.1</v>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
@@ -4737,8 +5105,10 @@
           <t>Android Appium Forms Spec #29</t>
         </is>
       </c>
-      <c r="D186" s="4" t="n">
-        <v>0.12</v>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
@@ -4760,8 +5130,10 @@
           <t>Android Appium Forms Spec #30</t>
         </is>
       </c>
-      <c r="D187" s="4" t="n">
-        <v>0.04</v>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
@@ -4783,8 +5155,10 @@
           <t>Android Appium Forms Spec #31</t>
         </is>
       </c>
-      <c r="D188" s="4" t="n">
-        <v>0.06</v>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
@@ -4806,8 +5180,10 @@
           <t>Android Appium Forms Spec #32</t>
         </is>
       </c>
-      <c r="D189" s="4" t="n">
-        <v>0.08</v>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
@@ -4829,8 +5205,10 @@
           <t>Android Appium Forms Spec #33</t>
         </is>
       </c>
-      <c r="D190" s="4" t="n">
-        <v>0.1</v>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
@@ -4852,8 +5230,10 @@
           <t>Android Appium Forms Spec #34</t>
         </is>
       </c>
-      <c r="D191" s="4" t="n">
-        <v>0.12</v>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
@@ -4875,8 +5255,10 @@
           <t>Android Appium Forms Spec #35</t>
         </is>
       </c>
-      <c r="D192" s="4" t="n">
-        <v>0.04</v>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
@@ -4898,8 +5280,10 @@
           <t>Android Appium Forms Spec #36</t>
         </is>
       </c>
-      <c r="D193" s="4" t="n">
-        <v>0.06</v>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
@@ -4921,8 +5305,10 @@
           <t>Android Appium Forms Spec #37</t>
         </is>
       </c>
-      <c r="D194" s="4" t="n">
-        <v>0.08</v>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
@@ -4944,8 +5330,10 @@
           <t>Android Appium Forms Spec #38</t>
         </is>
       </c>
-      <c r="D195" s="4" t="n">
-        <v>0.1</v>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
@@ -4967,8 +5355,10 @@
           <t>Android Appium Forms Spec #39</t>
         </is>
       </c>
-      <c r="D196" s="4" t="n">
-        <v>0.12</v>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -4990,8 +5380,10 @@
           <t>Android Appium CRUD Operations Spec #01</t>
         </is>
       </c>
-      <c r="D197" s="4" t="n">
-        <v>0.06</v>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
@@ -5013,8 +5405,10 @@
           <t>Android Appium CRUD Operations Spec #02</t>
         </is>
       </c>
-      <c r="D198" s="4" t="n">
-        <v>0.08</v>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
@@ -5036,8 +5430,10 @@
           <t>Android Appium CRUD Operations Spec #03</t>
         </is>
       </c>
-      <c r="D199" s="4" t="n">
-        <v>0.1</v>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -5059,8 +5455,10 @@
           <t>Android Appium CRUD Operations Spec #04</t>
         </is>
       </c>
-      <c r="D200" s="4" t="n">
-        <v>0.12</v>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
@@ -5082,8 +5480,10 @@
           <t>Android Appium CRUD Operations Spec #05</t>
         </is>
       </c>
-      <c r="D201" s="4" t="n">
-        <v>0.04</v>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -5105,8 +5505,10 @@
           <t>Android Appium CRUD Operations Spec #06</t>
         </is>
       </c>
-      <c r="D202" s="4" t="n">
-        <v>0.06</v>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
@@ -5128,8 +5530,10 @@
           <t>Android Appium CRUD Operations Spec #07</t>
         </is>
       </c>
-      <c r="D203" s="4" t="n">
-        <v>0.08</v>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
@@ -5151,8 +5555,10 @@
           <t>Android Appium CRUD Operations Spec #08</t>
         </is>
       </c>
-      <c r="D204" s="4" t="n">
-        <v>0.1</v>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
@@ -5174,8 +5580,10 @@
           <t>Android Appium CRUD Operations Spec #09</t>
         </is>
       </c>
-      <c r="D205" s="4" t="n">
-        <v>0.12</v>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -5197,8 +5605,10 @@
           <t>Android Appium CRUD Operations Spec #10</t>
         </is>
       </c>
-      <c r="D206" s="4" t="n">
-        <v>0.04</v>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
@@ -5220,8 +5630,10 @@
           <t>Android Appium CRUD Operations Spec #11</t>
         </is>
       </c>
-      <c r="D207" s="4" t="n">
-        <v>0.06</v>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
@@ -5243,8 +5655,10 @@
           <t>Android Appium CRUD Operations Spec #12</t>
         </is>
       </c>
-      <c r="D208" s="4" t="n">
-        <v>0.08</v>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
@@ -5266,8 +5680,10 @@
           <t>Android Appium CRUD Operations Spec #13</t>
         </is>
       </c>
-      <c r="D209" s="4" t="n">
-        <v>0.1</v>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
@@ -5289,8 +5705,10 @@
           <t>Android Appium CRUD Operations Spec #14</t>
         </is>
       </c>
-      <c r="D210" s="4" t="n">
-        <v>0.12</v>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
@@ -5312,8 +5730,10 @@
           <t>Android Appium CRUD Operations Spec #15</t>
         </is>
       </c>
-      <c r="D211" s="4" t="n">
-        <v>0.04</v>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
@@ -5335,8 +5755,10 @@
           <t>Android Appium CRUD Operations Spec #16</t>
         </is>
       </c>
-      <c r="D212" s="4" t="n">
-        <v>0.06</v>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
@@ -5358,8 +5780,10 @@
           <t>Android Appium CRUD Operations Spec #17</t>
         </is>
       </c>
-      <c r="D213" s="4" t="n">
-        <v>0.08</v>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
@@ -5381,8 +5805,10 @@
           <t>Android Appium CRUD Operations Spec #18</t>
         </is>
       </c>
-      <c r="D214" s="4" t="n">
-        <v>0.1</v>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
@@ -5404,8 +5830,10 @@
           <t>Android Appium CRUD Operations Spec #19</t>
         </is>
       </c>
-      <c r="D215" s="4" t="n">
-        <v>0.12</v>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
@@ -5427,8 +5855,10 @@
           <t>Android Appium CRUD Operations Spec #20</t>
         </is>
       </c>
-      <c r="D216" s="4" t="n">
-        <v>0.04</v>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
@@ -5450,8 +5880,10 @@
           <t>Android Appium CRUD Operations Spec #21</t>
         </is>
       </c>
-      <c r="D217" s="4" t="n">
-        <v>0.06</v>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -5473,8 +5905,10 @@
           <t>Android Appium CRUD Operations Spec #22</t>
         </is>
       </c>
-      <c r="D218" s="4" t="n">
-        <v>0.08</v>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
@@ -5496,8 +5930,10 @@
           <t>Android Appium CRUD Operations Spec #23</t>
         </is>
       </c>
-      <c r="D219" s="4" t="n">
-        <v>0.1</v>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
@@ -5519,8 +5955,10 @@
           <t>Android Appium CRUD Operations Spec #24</t>
         </is>
       </c>
-      <c r="D220" s="4" t="n">
-        <v>0.12</v>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
@@ -5542,8 +5980,10 @@
           <t>Android Appium CRUD Operations Spec #25</t>
         </is>
       </c>
-      <c r="D221" s="4" t="n">
-        <v>0.04</v>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
@@ -5565,8 +6005,10 @@
           <t>Android Appium CRUD Operations Spec #26</t>
         </is>
       </c>
-      <c r="D222" s="4" t="n">
-        <v>0.06</v>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
@@ -5588,8 +6030,10 @@
           <t>Android Appium CRUD Operations Spec #27</t>
         </is>
       </c>
-      <c r="D223" s="4" t="n">
-        <v>0.08</v>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
@@ -5611,8 +6055,10 @@
           <t>Android Appium CRUD Operations Spec #28</t>
         </is>
       </c>
-      <c r="D224" s="4" t="n">
-        <v>0.1</v>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
@@ -5634,8 +6080,10 @@
           <t>Android Appium CRUD Operations Spec #29</t>
         </is>
       </c>
-      <c r="D225" s="4" t="n">
-        <v>0.12</v>
+      <c r="D225" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
@@ -5657,8 +6105,10 @@
           <t>Android Appium CRUD Operations Spec #30</t>
         </is>
       </c>
-      <c r="D226" s="4" t="n">
-        <v>0.04</v>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
@@ -5680,8 +6130,10 @@
           <t>Android Appium CRUD Operations Spec #31</t>
         </is>
       </c>
-      <c r="D227" s="4" t="n">
-        <v>0.06</v>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -5703,8 +6155,10 @@
           <t>Android Appium CRUD Operations Spec #32</t>
         </is>
       </c>
-      <c r="D228" s="4" t="n">
-        <v>0.08</v>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
@@ -5726,8 +6180,10 @@
           <t>Android Appium CRUD Operations Spec #33</t>
         </is>
       </c>
-      <c r="D229" s="4" t="n">
-        <v>0.1</v>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
@@ -5749,8 +6205,10 @@
           <t>Android Appium CRUD Operations Spec #34</t>
         </is>
       </c>
-      <c r="D230" s="4" t="n">
-        <v>0.12</v>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -5772,8 +6230,10 @@
           <t>Android Appium CRUD Operations Spec #35</t>
         </is>
       </c>
-      <c r="D231" s="4" t="n">
-        <v>0.04</v>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
@@ -5795,8 +6255,10 @@
           <t>Android Appium CRUD Operations Spec #36</t>
         </is>
       </c>
-      <c r="D232" s="4" t="n">
-        <v>0.06</v>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
@@ -5818,8 +6280,10 @@
           <t>Android Appium CRUD Operations Spec #37</t>
         </is>
       </c>
-      <c r="D233" s="4" t="n">
-        <v>0.08</v>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
@@ -5841,8 +6305,10 @@
           <t>Android Appium CRUD Operations Spec #38</t>
         </is>
       </c>
-      <c r="D234" s="4" t="n">
-        <v>0.1</v>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
@@ -5864,8 +6330,10 @@
           <t>Android Appium CRUD Operations Spec #39</t>
         </is>
       </c>
-      <c r="D235" s="4" t="n">
-        <v>0.12</v>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -5887,8 +6355,10 @@
           <t>Android Appium Search Spec #01</t>
         </is>
       </c>
-      <c r="D236" s="4" t="n">
-        <v>0.06</v>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -5910,8 +6380,10 @@
           <t>Android Appium Search Spec #02</t>
         </is>
       </c>
-      <c r="D237" s="4" t="n">
-        <v>0.08</v>
+      <c r="D237" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
@@ -5933,8 +6405,10 @@
           <t>Android Appium Search Spec #03</t>
         </is>
       </c>
-      <c r="D238" s="4" t="n">
-        <v>0.1</v>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -5956,8 +6430,10 @@
           <t>Android Appium Search Spec #04</t>
         </is>
       </c>
-      <c r="D239" s="4" t="n">
-        <v>0.12</v>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
@@ -5979,8 +6455,10 @@
           <t>Android Appium Search Spec #05</t>
         </is>
       </c>
-      <c r="D240" s="4" t="n">
-        <v>0.04</v>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -6002,8 +6480,10 @@
           <t>Android Appium Search Spec #06</t>
         </is>
       </c>
-      <c r="D241" s="4" t="n">
-        <v>0.06</v>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -6025,8 +6505,10 @@
           <t>Android Appium Search Spec #07</t>
         </is>
       </c>
-      <c r="D242" s="4" t="n">
-        <v>0.08</v>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -6048,8 +6530,10 @@
           <t>Android Appium Search Spec #08</t>
         </is>
       </c>
-      <c r="D243" s="4" t="n">
-        <v>0.1</v>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -6071,8 +6555,10 @@
           <t>Android Appium Search Spec #09</t>
         </is>
       </c>
-      <c r="D244" s="4" t="n">
-        <v>0.12</v>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
@@ -6094,8 +6580,10 @@
           <t>Android Appium Search Spec #10</t>
         </is>
       </c>
-      <c r="D245" s="4" t="n">
-        <v>0.04</v>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
@@ -6117,8 +6605,10 @@
           <t>Android Appium Search Spec #11</t>
         </is>
       </c>
-      <c r="D246" s="4" t="n">
-        <v>0.06</v>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
@@ -6140,8 +6630,10 @@
           <t>Android Appium Search Spec #12</t>
         </is>
       </c>
-      <c r="D247" s="4" t="n">
-        <v>0.08</v>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
@@ -6163,8 +6655,10 @@
           <t>Android Appium Search Spec #13</t>
         </is>
       </c>
-      <c r="D248" s="4" t="n">
-        <v>0.1</v>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -6186,8 +6680,10 @@
           <t>Android Appium Search Spec #14</t>
         </is>
       </c>
-      <c r="D249" s="4" t="n">
-        <v>0.12</v>
+      <c r="D249" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
@@ -6209,8 +6705,10 @@
           <t>Android Appium Search Spec #15</t>
         </is>
       </c>
-      <c r="D250" s="4" t="n">
-        <v>0.04</v>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
@@ -6232,8 +6730,10 @@
           <t>Android Appium Search Spec #16</t>
         </is>
       </c>
-      <c r="D251" s="4" t="n">
-        <v>0.06</v>
+      <c r="D251" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
@@ -6255,8 +6755,10 @@
           <t>Android Appium Search Spec #17</t>
         </is>
       </c>
-      <c r="D252" s="4" t="n">
-        <v>0.08</v>
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
@@ -6278,8 +6780,10 @@
           <t>Android Appium Search Spec #18</t>
         </is>
       </c>
-      <c r="D253" s="4" t="n">
-        <v>0.1</v>
+      <c r="D253" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
@@ -6301,8 +6805,10 @@
           <t>Android Appium Search Spec #19</t>
         </is>
       </c>
-      <c r="D254" s="4" t="n">
-        <v>0.12</v>
+      <c r="D254" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -6324,8 +6830,10 @@
           <t>Android Appium Search Spec #20</t>
         </is>
       </c>
-      <c r="D255" s="4" t="n">
-        <v>0.04</v>
+      <c r="D255" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
@@ -6347,8 +6855,10 @@
           <t>Android Appium Filters Spec #01</t>
         </is>
       </c>
-      <c r="D256" s="4" t="n">
-        <v>0.06</v>
+      <c r="D256" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
@@ -6370,8 +6880,10 @@
           <t>Android Appium Filters Spec #02</t>
         </is>
       </c>
-      <c r="D257" s="4" t="n">
-        <v>0.08</v>
+      <c r="D257" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
@@ -6393,8 +6905,10 @@
           <t>Android Appium Filters Spec #03</t>
         </is>
       </c>
-      <c r="D258" s="4" t="n">
-        <v>0.1</v>
+      <c r="D258" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
@@ -6416,8 +6930,10 @@
           <t>Android Appium Filters Spec #04</t>
         </is>
       </c>
-      <c r="D259" s="4" t="n">
-        <v>0.12</v>
+      <c r="D259" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
@@ -6439,8 +6955,10 @@
           <t>Android Appium Filters Spec #05</t>
         </is>
       </c>
-      <c r="D260" s="4" t="n">
-        <v>0.04</v>
+      <c r="D260" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -6462,8 +6980,10 @@
           <t>Android Appium Filters Spec #06</t>
         </is>
       </c>
-      <c r="D261" s="4" t="n">
-        <v>0.06</v>
+      <c r="D261" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -6485,8 +7005,10 @@
           <t>Android Appium Filters Spec #07</t>
         </is>
       </c>
-      <c r="D262" s="4" t="n">
-        <v>0.08</v>
+      <c r="D262" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -6508,8 +7030,10 @@
           <t>Android Appium Filters Spec #08</t>
         </is>
       </c>
-      <c r="D263" s="4" t="n">
-        <v>0.1</v>
+      <c r="D263" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
@@ -6531,8 +7055,10 @@
           <t>Android Appium Filters Spec #09</t>
         </is>
       </c>
-      <c r="D264" s="4" t="n">
-        <v>0.12</v>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
@@ -6554,8 +7080,10 @@
           <t>Android Appium Filters Spec #10</t>
         </is>
       </c>
-      <c r="D265" s="4" t="n">
-        <v>0.04</v>
+      <c r="D265" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -6577,8 +7105,10 @@
           <t>Android Appium Filters Spec #11</t>
         </is>
       </c>
-      <c r="D266" s="4" t="n">
-        <v>0.06</v>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -6600,8 +7130,10 @@
           <t>Android Appium Filters Spec #12</t>
         </is>
       </c>
-      <c r="D267" s="4" t="n">
-        <v>0.08</v>
+      <c r="D267" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -6623,8 +7155,10 @@
           <t>Android Appium Filters Spec #13</t>
         </is>
       </c>
-      <c r="D268" s="4" t="n">
-        <v>0.1</v>
+      <c r="D268" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -6646,8 +7180,10 @@
           <t>Android Appium Filters Spec #14</t>
         </is>
       </c>
-      <c r="D269" s="4" t="n">
-        <v>0.12</v>
+      <c r="D269" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
@@ -6669,8 +7205,10 @@
           <t>Android Appium Filters Spec #15</t>
         </is>
       </c>
-      <c r="D270" s="4" t="n">
-        <v>0.04</v>
+      <c r="D270" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
@@ -6692,8 +7230,10 @@
           <t>Android Appium Filters Spec #16</t>
         </is>
       </c>
-      <c r="D271" s="4" t="n">
-        <v>0.06</v>
+      <c r="D271" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -6715,8 +7255,10 @@
           <t>Android Appium Filters Spec #17</t>
         </is>
       </c>
-      <c r="D272" s="4" t="n">
-        <v>0.08</v>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
@@ -6738,8 +7280,10 @@
           <t>Android Appium Filters Spec #18</t>
         </is>
       </c>
-      <c r="D273" s="4" t="n">
-        <v>0.1</v>
+      <c r="D273" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -6761,8 +7305,10 @@
           <t>Android Appium Filters Spec #19</t>
         </is>
       </c>
-      <c r="D274" s="4" t="n">
-        <v>0.12</v>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
@@ -6784,8 +7330,10 @@
           <t>Android Appium Input Validation Spec #01</t>
         </is>
       </c>
-      <c r="D275" s="4" t="n">
-        <v>0.06</v>
+      <c r="D275" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
@@ -6807,8 +7355,10 @@
           <t>Android Appium Input Validation Spec #02</t>
         </is>
       </c>
-      <c r="D276" s="4" t="n">
-        <v>0.08</v>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -6830,8 +7380,10 @@
           <t>Android Appium Input Validation Spec #03</t>
         </is>
       </c>
-      <c r="D277" s="4" t="n">
-        <v>0.1</v>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -6853,8 +7405,10 @@
           <t>Android Appium Input Validation Spec #04</t>
         </is>
       </c>
-      <c r="D278" s="4" t="n">
-        <v>0.12</v>
+      <c r="D278" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
@@ -6876,8 +7430,10 @@
           <t>Android Appium Input Validation Spec #05</t>
         </is>
       </c>
-      <c r="D279" s="4" t="n">
-        <v>0.04</v>
+      <c r="D279" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
@@ -6899,8 +7455,10 @@
           <t>Android Appium Input Validation Spec #06</t>
         </is>
       </c>
-      <c r="D280" s="4" t="n">
-        <v>0.06</v>
+      <c r="D280" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
@@ -6922,8 +7480,10 @@
           <t>Android Appium Input Validation Spec #07</t>
         </is>
       </c>
-      <c r="D281" s="4" t="n">
-        <v>0.08</v>
+      <c r="D281" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
@@ -6945,8 +7505,10 @@
           <t>Android Appium Input Validation Spec #08</t>
         </is>
       </c>
-      <c r="D282" s="4" t="n">
-        <v>0.1</v>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
@@ -6968,8 +7530,10 @@
           <t>Android Appium Input Validation Spec #09</t>
         </is>
       </c>
-      <c r="D283" s="4" t="n">
-        <v>0.12</v>
+      <c r="D283" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
@@ -6991,8 +7555,10 @@
           <t>Android Appium Input Validation Spec #10</t>
         </is>
       </c>
-      <c r="D284" s="4" t="n">
-        <v>0.04</v>
+      <c r="D284" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -7014,8 +7580,10 @@
           <t>Android Appium Input Validation Spec #11</t>
         </is>
       </c>
-      <c r="D285" s="4" t="n">
-        <v>0.06</v>
+      <c r="D285" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -7037,8 +7605,10 @@
           <t>Android Appium Input Validation Spec #12</t>
         </is>
       </c>
-      <c r="D286" s="4" t="n">
-        <v>0.08</v>
+      <c r="D286" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
@@ -7060,8 +7630,10 @@
           <t>Android Appium Input Validation Spec #13</t>
         </is>
       </c>
-      <c r="D287" s="4" t="n">
-        <v>0.1</v>
+      <c r="D287" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
@@ -7083,8 +7655,10 @@
           <t>Android Appium Input Validation Spec #14</t>
         </is>
       </c>
-      <c r="D288" s="4" t="n">
-        <v>0.12</v>
+      <c r="D288" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
@@ -7106,8 +7680,10 @@
           <t>Android Appium Input Validation Spec #15</t>
         </is>
       </c>
-      <c r="D289" s="4" t="n">
-        <v>0.04</v>
+      <c r="D289" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
@@ -7129,8 +7705,10 @@
           <t>Android Appium Input Validation Spec #16</t>
         </is>
       </c>
-      <c r="D290" s="4" t="n">
-        <v>0.06</v>
+      <c r="D290" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
@@ -7152,8 +7730,10 @@
           <t>Android Appium Input Validation Spec #17</t>
         </is>
       </c>
-      <c r="D291" s="4" t="n">
-        <v>0.08</v>
+      <c r="D291" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
@@ -7175,8 +7755,10 @@
           <t>Android Appium Input Validation Spec #18</t>
         </is>
       </c>
-      <c r="D292" s="4" t="n">
-        <v>0.1</v>
+      <c r="D292" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -7198,8 +7780,10 @@
           <t>Android Appium Input Validation Spec #19</t>
         </is>
       </c>
-      <c r="D293" s="4" t="n">
-        <v>0.12</v>
+      <c r="D293" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
@@ -7221,8 +7805,10 @@
           <t>Android Appium Input Validation Spec #20</t>
         </is>
       </c>
-      <c r="D294" s="4" t="n">
-        <v>0.04</v>
+      <c r="D294" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -7244,8 +7830,10 @@
           <t>Android Appium Input Validation Spec #21</t>
         </is>
       </c>
-      <c r="D295" s="4" t="n">
-        <v>0.06</v>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
@@ -7267,8 +7855,10 @@
           <t>Android Appium Input Validation Spec #22</t>
         </is>
       </c>
-      <c r="D296" s="4" t="n">
-        <v>0.08</v>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -7290,8 +7880,10 @@
           <t>Android Appium Input Validation Spec #23</t>
         </is>
       </c>
-      <c r="D297" s="4" t="n">
-        <v>0.1</v>
+      <c r="D297" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -7313,8 +7905,10 @@
           <t>Android Appium Input Validation Spec #24</t>
         </is>
       </c>
-      <c r="D298" s="4" t="n">
-        <v>0.12</v>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -7336,8 +7930,10 @@
           <t>Android Appium Input Validation Spec #25</t>
         </is>
       </c>
-      <c r="D299" s="4" t="n">
-        <v>0.04</v>
+      <c r="D299" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -7359,8 +7955,10 @@
           <t>Android Appium Input Validation Spec #26</t>
         </is>
       </c>
-      <c r="D300" s="4" t="n">
-        <v>0.06</v>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -7382,8 +7980,10 @@
           <t>Android Appium Input Validation Spec #27</t>
         </is>
       </c>
-      <c r="D301" s="4" t="n">
-        <v>0.08</v>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -7405,8 +8005,10 @@
           <t>Android Appium Input Validation Spec #28</t>
         </is>
       </c>
-      <c r="D302" s="4" t="n">
-        <v>0.1</v>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
@@ -7428,8 +8030,10 @@
           <t>Android Appium Input Validation Spec #29</t>
         </is>
       </c>
-      <c r="D303" s="4" t="n">
-        <v>0.12</v>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -7451,8 +8055,10 @@
           <t>Android Appium Input Validation Spec #30</t>
         </is>
       </c>
-      <c r="D304" s="4" t="n">
-        <v>0.04</v>
+      <c r="D304" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -7474,8 +8080,10 @@
           <t>Android Appium Input Validation Spec #31</t>
         </is>
       </c>
-      <c r="D305" s="4" t="n">
-        <v>0.06</v>
+      <c r="D305" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
@@ -7497,8 +8105,10 @@
           <t>Android Appium Input Validation Spec #32</t>
         </is>
       </c>
-      <c r="D306" s="4" t="n">
-        <v>0.08</v>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
@@ -7520,8 +8130,10 @@
           <t>Android Appium Input Validation Spec #33</t>
         </is>
       </c>
-      <c r="D307" s="4" t="n">
-        <v>0.1</v>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
@@ -7543,8 +8155,10 @@
           <t>Android Appium Input Validation Spec #34</t>
         </is>
       </c>
-      <c r="D308" s="4" t="n">
-        <v>0.12</v>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
@@ -7566,8 +8180,10 @@
           <t>Android Appium Input Validation Spec #35</t>
         </is>
       </c>
-      <c r="D309" s="4" t="n">
-        <v>0.04</v>
+      <c r="D309" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
@@ -7589,8 +8205,10 @@
           <t>Android Appium Input Validation Spec #36</t>
         </is>
       </c>
-      <c r="D310" s="4" t="n">
-        <v>0.06</v>
+      <c r="D310" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
@@ -7612,8 +8230,10 @@
           <t>Android Appium Input Validation Spec #37</t>
         </is>
       </c>
-      <c r="D311" s="4" t="n">
-        <v>0.08</v>
+      <c r="D311" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
@@ -7635,8 +8255,10 @@
           <t>Android Appium Input Validation Spec #38</t>
         </is>
       </c>
-      <c r="D312" s="4" t="n">
-        <v>0.1</v>
+      <c r="D312" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
@@ -7658,8 +8280,10 @@
           <t>Android Appium Input Validation Spec #39</t>
         </is>
       </c>
-      <c r="D313" s="4" t="n">
-        <v>0.12</v>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -7681,8 +8305,10 @@
           <t>Android Appium Error Handling Spec #01</t>
         </is>
       </c>
-      <c r="D314" s="4" t="n">
-        <v>0.06</v>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
@@ -7704,8 +8330,10 @@
           <t>Android Appium Error Handling Spec #02</t>
         </is>
       </c>
-      <c r="D315" s="4" t="n">
-        <v>0.08</v>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -7727,8 +8355,10 @@
           <t>Android Appium Error Handling Spec #03</t>
         </is>
       </c>
-      <c r="D316" s="4" t="n">
-        <v>0.1</v>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -7750,8 +8380,10 @@
           <t>Android Appium Error Handling Spec #04</t>
         </is>
       </c>
-      <c r="D317" s="4" t="n">
-        <v>0.12</v>
+      <c r="D317" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -7773,8 +8405,10 @@
           <t>Android Appium Error Handling Spec #05</t>
         </is>
       </c>
-      <c r="D318" s="4" t="n">
-        <v>0.04</v>
+      <c r="D318" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
@@ -7796,8 +8430,10 @@
           <t>Android Appium Error Handling Spec #06</t>
         </is>
       </c>
-      <c r="D319" s="4" t="n">
-        <v>0.06</v>
+      <c r="D319" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
@@ -7819,8 +8455,10 @@
           <t>Android Appium Error Handling Spec #07</t>
         </is>
       </c>
-      <c r="D320" s="4" t="n">
-        <v>0.08</v>
+      <c r="D320" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
@@ -7842,8 +8480,10 @@
           <t>Android Appium Error Handling Spec #08</t>
         </is>
       </c>
-      <c r="D321" s="4" t="n">
-        <v>0.1</v>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
@@ -7865,8 +8505,10 @@
           <t>Android Appium Error Handling Spec #09</t>
         </is>
       </c>
-      <c r="D322" s="4" t="n">
-        <v>0.12</v>
+      <c r="D322" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
@@ -7888,8 +8530,10 @@
           <t>Android Appium Error Handling Spec #10</t>
         </is>
       </c>
-      <c r="D323" s="4" t="n">
-        <v>0.04</v>
+      <c r="D323" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -7911,8 +8555,10 @@
           <t>Android Appium Error Handling Spec #11</t>
         </is>
       </c>
-      <c r="D324" s="4" t="n">
-        <v>0.06</v>
+      <c r="D324" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
@@ -7934,8 +8580,10 @@
           <t>Android Appium Error Handling Spec #12</t>
         </is>
       </c>
-      <c r="D325" s="4" t="n">
-        <v>0.08</v>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -7957,8 +8605,10 @@
           <t>Android Appium Error Handling Spec #13</t>
         </is>
       </c>
-      <c r="D326" s="4" t="n">
-        <v>0.1</v>
+      <c r="D326" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
@@ -7980,8 +8630,10 @@
           <t>Android Appium Error Handling Spec #14</t>
         </is>
       </c>
-      <c r="D327" s="4" t="n">
-        <v>0.12</v>
+      <c r="D327" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
@@ -8003,8 +8655,10 @@
           <t>Android Appium Error Handling Spec #15</t>
         </is>
       </c>
-      <c r="D328" s="4" t="n">
-        <v>0.04</v>
+      <c r="D328" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
@@ -8026,8 +8680,10 @@
           <t>Android Appium Error Handling Spec #16</t>
         </is>
       </c>
-      <c r="D329" s="4" t="n">
-        <v>0.06</v>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
@@ -8049,8 +8705,10 @@
           <t>Android Appium Error Handling Spec #17</t>
         </is>
       </c>
-      <c r="D330" s="4" t="n">
-        <v>0.08</v>
+      <c r="D330" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -8072,8 +8730,10 @@
           <t>Android Appium Error Handling Spec #18</t>
         </is>
       </c>
-      <c r="D331" s="4" t="n">
-        <v>0.1</v>
+      <c r="D331" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -8095,8 +8755,10 @@
           <t>Android Appium Error Handling Spec #19</t>
         </is>
       </c>
-      <c r="D332" s="4" t="n">
-        <v>0.12</v>
+      <c r="D332" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
@@ -8118,8 +8780,10 @@
           <t>Android Appium Error Handling Spec #20</t>
         </is>
       </c>
-      <c r="D333" s="4" t="n">
-        <v>0.04</v>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
@@ -8141,8 +8805,10 @@
           <t>Android Appium Session Management Spec #01</t>
         </is>
       </c>
-      <c r="D334" s="4" t="n">
-        <v>0.06</v>
+      <c r="D334" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
@@ -8164,8 +8830,10 @@
           <t>Android Appium Session Management Spec #02</t>
         </is>
       </c>
-      <c r="D335" s="4" t="n">
-        <v>0.08</v>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
@@ -8187,8 +8855,10 @@
           <t>Android Appium Session Management Spec #03</t>
         </is>
       </c>
-      <c r="D336" s="4" t="n">
-        <v>0.1</v>
+      <c r="D336" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
@@ -8210,8 +8880,10 @@
           <t>Android Appium Session Management Spec #04</t>
         </is>
       </c>
-      <c r="D337" s="4" t="n">
-        <v>0.12</v>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
@@ -8233,8 +8905,10 @@
           <t>Android Appium Session Management Spec #05</t>
         </is>
       </c>
-      <c r="D338" s="4" t="n">
-        <v>0.04</v>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
@@ -8256,8 +8930,10 @@
           <t>Android Appium Session Management Spec #06</t>
         </is>
       </c>
-      <c r="D339" s="4" t="n">
-        <v>0.06</v>
+      <c r="D339" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
@@ -8279,8 +8955,10 @@
           <t>Android Appium Session Management Spec #07</t>
         </is>
       </c>
-      <c r="D340" s="4" t="n">
-        <v>0.08</v>
+      <c r="D340" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
@@ -8302,8 +8980,10 @@
           <t>Android Appium Session Management Spec #08</t>
         </is>
       </c>
-      <c r="D341" s="4" t="n">
-        <v>0.1</v>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
@@ -8325,8 +9005,10 @@
           <t>Android Appium Session Management Spec #09</t>
         </is>
       </c>
-      <c r="D342" s="4" t="n">
-        <v>0.12</v>
+      <c r="D342" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
@@ -8348,8 +9030,10 @@
           <t>Android Appium Session Management Spec #10</t>
         </is>
       </c>
-      <c r="D343" s="4" t="n">
-        <v>0.04</v>
+      <c r="D343" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
@@ -8371,8 +9055,10 @@
           <t>Android Appium Session Management Spec #11</t>
         </is>
       </c>
-      <c r="D344" s="4" t="n">
-        <v>0.06</v>
+      <c r="D344" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
@@ -8394,8 +9080,10 @@
           <t>Android Appium Session Management Spec #12</t>
         </is>
       </c>
-      <c r="D345" s="4" t="n">
-        <v>0.08</v>
+      <c r="D345" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
@@ -8417,8 +9105,10 @@
           <t>Android Appium Session Management Spec #13</t>
         </is>
       </c>
-      <c r="D346" s="4" t="n">
-        <v>0.1</v>
+      <c r="D346" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
@@ -8440,8 +9130,10 @@
           <t>Android Appium Session Management Spec #14</t>
         </is>
       </c>
-      <c r="D347" s="4" t="n">
-        <v>0.12</v>
+      <c r="D347" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
@@ -8463,8 +9155,10 @@
           <t>Android Appium Session Management Spec #15</t>
         </is>
       </c>
-      <c r="D348" s="4" t="n">
-        <v>0.04</v>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
@@ -8486,8 +9180,10 @@
           <t>Android Appium Session Management Spec #16</t>
         </is>
       </c>
-      <c r="D349" s="4" t="n">
-        <v>0.06</v>
+      <c r="D349" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -8509,8 +9205,10 @@
           <t>Android Appium Session Management Spec #17</t>
         </is>
       </c>
-      <c r="D350" s="4" t="n">
-        <v>0.08</v>
+      <c r="D350" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
@@ -8532,8 +9230,10 @@
           <t>Android Appium Session Management Spec #18</t>
         </is>
       </c>
-      <c r="D351" s="4" t="n">
-        <v>0.1</v>
+      <c r="D351" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
@@ -8555,8 +9255,10 @@
           <t>Android Appium Session Management Spec #19</t>
         </is>
       </c>
-      <c r="D352" s="4" t="n">
-        <v>0.12</v>
+      <c r="D352" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -8578,8 +9280,10 @@
           <t>Android Appium Notifications Spec #01</t>
         </is>
       </c>
-      <c r="D353" s="4" t="n">
-        <v>0.06</v>
+      <c r="D353" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -8601,8 +9305,10 @@
           <t>Android Appium Notifications Spec #02</t>
         </is>
       </c>
-      <c r="D354" s="4" t="n">
-        <v>0.08</v>
+      <c r="D354" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
@@ -8624,8 +9330,10 @@
           <t>Android Appium Notifications Spec #03</t>
         </is>
       </c>
-      <c r="D355" s="4" t="n">
-        <v>0.1</v>
+      <c r="D355" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
@@ -8647,8 +9355,10 @@
           <t>Android Appium Notifications Spec #04</t>
         </is>
       </c>
-      <c r="D356" s="4" t="n">
-        <v>0.12</v>
+      <c r="D356" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -8670,8 +9380,10 @@
           <t>Android Appium Notifications Spec #05</t>
         </is>
       </c>
-      <c r="D357" s="4" t="n">
-        <v>0.04</v>
+      <c r="D357" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
@@ -8693,8 +9405,10 @@
           <t>Android Appium Notifications Spec #06</t>
         </is>
       </c>
-      <c r="D358" s="4" t="n">
-        <v>0.06</v>
+      <c r="D358" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
@@ -8716,8 +9430,10 @@
           <t>Android Appium Notifications Spec #07</t>
         </is>
       </c>
-      <c r="D359" s="4" t="n">
-        <v>0.08</v>
+      <c r="D359" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
@@ -8739,8 +9455,10 @@
           <t>Android Appium Notifications Spec #08</t>
         </is>
       </c>
-      <c r="D360" s="4" t="n">
-        <v>0.1</v>
+      <c r="D360" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
@@ -8762,8 +9480,10 @@
           <t>Android Appium Notifications Spec #09</t>
         </is>
       </c>
-      <c r="D361" s="4" t="n">
-        <v>0.12</v>
+      <c r="D361" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
@@ -8785,8 +9505,10 @@
           <t>Android Appium Notifications Spec #10</t>
         </is>
       </c>
-      <c r="D362" s="4" t="n">
-        <v>0.04</v>
+      <c r="D362" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
@@ -8808,8 +9530,10 @@
           <t>Android Appium File Upload Spec #01</t>
         </is>
       </c>
-      <c r="D363" s="4" t="n">
-        <v>0.06</v>
+      <c r="D363" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
@@ -8831,8 +9555,10 @@
           <t>Android Appium File Upload Spec #02</t>
         </is>
       </c>
-      <c r="D364" s="4" t="n">
-        <v>0.08</v>
+      <c r="D364" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
@@ -8854,8 +9580,10 @@
           <t>Android Appium File Upload Spec #03</t>
         </is>
       </c>
-      <c r="D365" s="4" t="n">
-        <v>0.1</v>
+      <c r="D365" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
@@ -8877,8 +9605,10 @@
           <t>Android Appium File Upload Spec #04</t>
         </is>
       </c>
-      <c r="D366" s="4" t="n">
-        <v>0.12</v>
+      <c r="D366" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
@@ -8900,8 +9630,10 @@
           <t>Android Appium File Upload Spec #05</t>
         </is>
       </c>
-      <c r="D367" s="4" t="n">
-        <v>0.04</v>
+      <c r="D367" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
@@ -8923,8 +9655,10 @@
           <t>Android Appium File Upload Spec #06</t>
         </is>
       </c>
-      <c r="D368" s="4" t="n">
-        <v>0.06</v>
+      <c r="D368" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
@@ -8946,8 +9680,10 @@
           <t>Android Appium File Upload Spec #07</t>
         </is>
       </c>
-      <c r="D369" s="4" t="n">
-        <v>0.08</v>
+      <c r="D369" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
@@ -8969,8 +9705,10 @@
           <t>Android Appium File Upload Spec #08</t>
         </is>
       </c>
-      <c r="D370" s="4" t="n">
-        <v>0.1</v>
+      <c r="D370" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
@@ -8992,8 +9730,10 @@
           <t>Android Appium File Upload Spec #09</t>
         </is>
       </c>
-      <c r="D371" s="4" t="n">
-        <v>0.12</v>
+      <c r="D371" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
@@ -9015,8 +9755,10 @@
           <t>Android Appium File Upload Spec #10</t>
         </is>
       </c>
-      <c r="D372" s="4" t="n">
-        <v>0.04</v>
+      <c r="D372" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
@@ -9038,8 +9780,10 @@
           <t>Android Appium Offline Handling Spec #01</t>
         </is>
       </c>
-      <c r="D373" s="4" t="n">
-        <v>0.06</v>
+      <c r="D373" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
@@ -9061,8 +9805,10 @@
           <t>Android Appium Offline Handling Spec #02</t>
         </is>
       </c>
-      <c r="D374" s="4" t="n">
-        <v>0.08</v>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
@@ -9084,8 +9830,10 @@
           <t>Android Appium Offline Handling Spec #03</t>
         </is>
       </c>
-      <c r="D375" s="4" t="n">
-        <v>0.1</v>
+      <c r="D375" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
@@ -9107,8 +9855,10 @@
           <t>Android Appium Offline Handling Spec #04</t>
         </is>
       </c>
-      <c r="D376" s="4" t="n">
-        <v>0.12</v>
+      <c r="D376" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
@@ -9130,8 +9880,10 @@
           <t>Android Appium Accessibility Spec #01</t>
         </is>
       </c>
-      <c r="D377" s="4" t="n">
-        <v>0.04</v>
+      <c r="D377" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
@@ -9153,8 +9905,10 @@
           <t>Android Appium Accessibility Spec #02</t>
         </is>
       </c>
-      <c r="D378" s="4" t="n">
-        <v>0.06</v>
+      <c r="D378" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
@@ -9176,8 +9930,10 @@
           <t>Android Appium Responsive UI Spec #01</t>
         </is>
       </c>
-      <c r="D379" s="4" t="n">
-        <v>0.08</v>
+      <c r="D379" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
@@ -9199,8 +9955,10 @@
           <t>Android Appium Responsive UI Spec #02</t>
         </is>
       </c>
-      <c r="D380" s="4" t="n">
-        <v>0.1</v>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
@@ -9222,8 +9980,10 @@
           <t>Android Appium Responsive UI Spec #03</t>
         </is>
       </c>
-      <c r="D381" s="4" t="n">
-        <v>0.12</v>
+      <c r="D381" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
@@ -9245,8 +10005,10 @@
           <t>Android Appium Responsive UI Spec #04</t>
         </is>
       </c>
-      <c r="D382" s="4" t="n">
-        <v>0.04</v>
+      <c r="D382" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
@@ -9268,8 +10030,10 @@
           <t>Android Appium Responsive UI Spec #05</t>
         </is>
       </c>
-      <c r="D383" s="4" t="n">
-        <v>0.06</v>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
@@ -9291,8 +10055,10 @@
           <t>Android Appium Responsive UI Spec #06</t>
         </is>
       </c>
-      <c r="D384" s="4" t="n">
-        <v>0.08</v>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
@@ -9314,8 +10080,10 @@
           <t>Android Appium Responsive UI Spec #07</t>
         </is>
       </c>
-      <c r="D385" s="4" t="n">
-        <v>0.1</v>
+      <c r="D385" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
@@ -9337,8 +10105,10 @@
           <t>Android Appium Responsive UI Spec #08</t>
         </is>
       </c>
-      <c r="D386" s="4" t="n">
-        <v>0.12</v>
+      <c r="D386" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
@@ -9360,8 +10130,10 @@
           <t>Android Appium Responsive UI Spec #09</t>
         </is>
       </c>
-      <c r="D387" s="4" t="n">
-        <v>0.04</v>
+      <c r="D387" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
@@ -9383,8 +10155,10 @@
           <t>Android Appium Responsive UI Spec #10</t>
         </is>
       </c>
-      <c r="D388" s="4" t="n">
-        <v>0.06</v>
+      <c r="D388" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
@@ -9406,8 +10180,10 @@
           <t>Android Appium Responsive UI Spec #11</t>
         </is>
       </c>
-      <c r="D389" s="4" t="n">
-        <v>0.08</v>
+      <c r="D389" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
@@ -9429,8 +10205,10 @@
           <t>Android Appium Performance Smoke Tests Spec #01</t>
         </is>
       </c>
-      <c r="D390" s="4" t="n">
-        <v>0.1</v>
+      <c r="D390" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
@@ -9452,10 +10230,212 @@
           <t>Android Appium Regression Suite Spec #01</t>
         </is>
       </c>
-      <c r="D391" s="4" t="n">
-        <v>0.12</v>
+      <c r="D391" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0391 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0392 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0393 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0394 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0395 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0396 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0397 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0398 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0399 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Workflow &amp; API Validation</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>TC_SENTINEL_0400 - Automated Security Verification Flow</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
